--- a/experiment/ELAN_bestx3/Test/results-Urban100/Urban100.xlsx
+++ b/experiment/ELAN_bestx3/Test/results-Urban100/Urban100.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25.73</v>
+        <v>29.61</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7116</v>
+        <v>0.8308</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24.58</v>
+        <v>29.22</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7451</v>
+        <v>0.8931</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22.78</v>
+        <v>25.61</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6384</v>
+        <v>0.7887</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22.96</v>
+        <v>25.45</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7842</v>
+        <v>0.9005</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25.09</v>
+        <v>31.93</v>
       </c>
       <c r="C6" t="n">
-        <v>0.833</v>
+        <v>0.974</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21.78</v>
+        <v>24.04</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5974</v>
+        <v>0.7085</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.26</v>
+        <v>32.15</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8305</v>
+        <v>0.9187</v>
       </c>
     </row>
     <row r="9">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>20.78</v>
+        <v>23.51</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6348</v>
+        <v>0.788</v>
       </c>
     </row>
     <row r="10">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>27.21</v>
+        <v>36.47</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7981</v>
+        <v>0.9537</v>
       </c>
     </row>
     <row r="11">
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>23.3</v>
+        <v>29.96</v>
       </c>
       <c r="C11" t="n">
-        <v>0.776</v>
+        <v>0.9308999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17.91</v>
+        <v>20.07</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7106</v>
+        <v>0.869</v>
       </c>
     </row>
     <row r="13">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>23.26</v>
+        <v>25.55</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6793</v>
+        <v>0.8244</v>
       </c>
     </row>
     <row r="14">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>27.16</v>
+        <v>31.55</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7446</v>
+        <v>0.8907</v>
       </c>
     </row>
     <row r="15">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>21.59</v>
+        <v>23.55</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6267</v>
+        <v>0.7716</v>
       </c>
     </row>
     <row r="16">
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>24.02</v>
+        <v>27.96</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6485</v>
+        <v>0.7907</v>
       </c>
     </row>
     <row r="17">
@@ -647,10 +647,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>26.42</v>
+        <v>33.48</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8247</v>
+        <v>0.9402</v>
       </c>
     </row>
     <row r="18">
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>24.1</v>
+        <v>27.96</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7584</v>
+        <v>0.897</v>
       </c>
     </row>
     <row r="19">
@@ -673,10 +673,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>25.88</v>
+        <v>27.64</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7143</v>
+        <v>0.7913</v>
       </c>
     </row>
     <row r="20">
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>20.53</v>
+        <v>24.73</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7184</v>
+        <v>0.8857</v>
       </c>
     </row>
     <row r="21">
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>21.55</v>
+        <v>24.11</v>
       </c>
       <c r="C21" t="n">
-        <v>0.6889</v>
+        <v>0.8144</v>
       </c>
     </row>
     <row r="22">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>26.76</v>
+        <v>31.66</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7359</v>
+        <v>0.8451</v>
       </c>
     </row>
     <row r="23">
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>25.76</v>
+        <v>27.38</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6768</v>
+        <v>0.8226</v>
       </c>
     </row>
     <row r="24">
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>27.96</v>
+        <v>33.58</v>
       </c>
       <c r="C24" t="n">
-        <v>0.8502</v>
+        <v>0.9555</v>
       </c>
     </row>
     <row r="25">
@@ -751,10 +751,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>19.51</v>
+        <v>23</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6027</v>
+        <v>0.7917</v>
       </c>
     </row>
     <row r="26">
@@ -764,10 +764,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>25.99</v>
+        <v>34.48</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7887999999999999</v>
+        <v>0.9317</v>
       </c>
     </row>
     <row r="27">
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>24.85</v>
+        <v>29.57</v>
       </c>
       <c r="C27" t="n">
-        <v>0.6152</v>
+        <v>0.7461</v>
       </c>
     </row>
     <row r="28">
@@ -790,10 +790,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>26.62</v>
+        <v>29.86</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7245</v>
+        <v>0.8526</v>
       </c>
     </row>
     <row r="29">
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>28.38</v>
+        <v>33.97</v>
       </c>
       <c r="C29" t="n">
-        <v>0.766</v>
+        <v>0.9137</v>
       </c>
     </row>
     <row r="30">
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>23.01</v>
+        <v>29.84</v>
       </c>
       <c r="C30" t="n">
-        <v>0.7329</v>
+        <v>0.9229000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>22.74</v>
+        <v>27.52</v>
       </c>
       <c r="C31" t="n">
-        <v>0.7333</v>
+        <v>0.9001</v>
       </c>
     </row>
     <row r="32">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>23.82</v>
+        <v>25.98</v>
       </c>
       <c r="C32" t="n">
-        <v>0.7364000000000001</v>
+        <v>0.8652</v>
       </c>
     </row>
     <row r="33">
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>25.69</v>
+        <v>31.47</v>
       </c>
       <c r="C33" t="n">
-        <v>0.7572</v>
+        <v>0.9139</v>
       </c>
     </row>
     <row r="34">
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>24.41</v>
+        <v>29.47</v>
       </c>
       <c r="C34" t="n">
-        <v>0.6821</v>
+        <v>0.8788</v>
       </c>
     </row>
     <row r="35">
@@ -881,10 +881,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>22.26</v>
+        <v>24.45</v>
       </c>
       <c r="C35" t="n">
-        <v>0.5849</v>
+        <v>0.6743</v>
       </c>
     </row>
     <row r="36">
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>25.1</v>
+        <v>31.61</v>
       </c>
       <c r="C36" t="n">
-        <v>0.767</v>
+        <v>0.9214</v>
       </c>
     </row>
     <row r="37">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>26.24</v>
+        <v>30.86</v>
       </c>
       <c r="C37" t="n">
-        <v>0.79</v>
+        <v>0.9254</v>
       </c>
     </row>
     <row r="38">
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>25.07</v>
+        <v>29.31</v>
       </c>
       <c r="C38" t="n">
-        <v>0.7794</v>
+        <v>0.885</v>
       </c>
     </row>
     <row r="39">
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>25.32</v>
+        <v>28.97</v>
       </c>
       <c r="C39" t="n">
-        <v>0.61</v>
+        <v>0.7809</v>
       </c>
     </row>
     <row r="40">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>21.25</v>
+        <v>25.26</v>
       </c>
       <c r="C40" t="n">
-        <v>0.6451</v>
+        <v>0.8446</v>
       </c>
     </row>
     <row r="41">
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>20.79</v>
+        <v>31.24</v>
       </c>
       <c r="C41" t="n">
-        <v>0.7423999999999999</v>
+        <v>0.9702</v>
       </c>
     </row>
     <row r="42">
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>22.56</v>
+        <v>30.21</v>
       </c>
       <c r="C42" t="n">
-        <v>0.7609</v>
+        <v>0.9384</v>
       </c>
     </row>
     <row r="43">
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>24.85</v>
+        <v>31.47</v>
       </c>
       <c r="C43" t="n">
-        <v>0.7966</v>
+        <v>0.9322</v>
       </c>
     </row>
     <row r="44">
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>24.43</v>
+        <v>34.83</v>
       </c>
       <c r="C44" t="n">
-        <v>0.8250999999999999</v>
+        <v>0.9543</v>
       </c>
     </row>
     <row r="45">
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>28.99</v>
+        <v>34.88</v>
       </c>
       <c r="C45" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.9346</v>
       </c>
     </row>
     <row r="46">
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>22.38</v>
+        <v>27.68</v>
       </c>
       <c r="C46" t="n">
-        <v>0.6776</v>
+        <v>0.8572</v>
       </c>
     </row>
     <row r="47">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>22.77</v>
+        <v>25.26</v>
       </c>
       <c r="C47" t="n">
-        <v>0.6961000000000001</v>
+        <v>0.8456</v>
       </c>
     </row>
     <row r="48">
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>20.89</v>
+        <v>23.98</v>
       </c>
       <c r="C48" t="n">
-        <v>0.6929</v>
+        <v>0.8623</v>
       </c>
     </row>
     <row r="49">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>19.53</v>
+        <v>23.02</v>
       </c>
       <c r="C49" t="n">
-        <v>0.7203000000000001</v>
+        <v>0.8997000000000001</v>
       </c>
     </row>
     <row r="50">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>21.9</v>
+        <v>25.82</v>
       </c>
       <c r="C50" t="n">
-        <v>0.6934</v>
+        <v>0.8375</v>
       </c>
     </row>
     <row r="51">
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>23.89</v>
+        <v>27.23</v>
       </c>
       <c r="C51" t="n">
-        <v>0.7282999999999999</v>
+        <v>0.8537</v>
       </c>
     </row>
     <row r="52">
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>25.61</v>
+        <v>29.92</v>
       </c>
       <c r="C52" t="n">
-        <v>0.7772</v>
+        <v>0.9103</v>
       </c>
     </row>
     <row r="53">
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>24.24</v>
+        <v>31.76</v>
       </c>
       <c r="C53" t="n">
-        <v>0.7756999999999999</v>
+        <v>0.946</v>
       </c>
     </row>
     <row r="54">
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>21.35</v>
+        <v>24.62</v>
       </c>
       <c r="C54" t="n">
-        <v>0.7025</v>
+        <v>0.8295</v>
       </c>
     </row>
     <row r="55">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>20.67</v>
+        <v>22.72</v>
       </c>
       <c r="C55" t="n">
-        <v>0.6161</v>
+        <v>0.7485000000000001</v>
       </c>
     </row>
     <row r="56">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>26.33</v>
+        <v>34.77</v>
       </c>
       <c r="C56" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.962</v>
       </c>
     </row>
     <row r="57">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>23.22</v>
+        <v>27.44</v>
       </c>
       <c r="C57" t="n">
-        <v>0.7257</v>
+        <v>0.8708</v>
       </c>
     </row>
     <row r="58">
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>27.17</v>
+        <v>34.05</v>
       </c>
       <c r="C58" t="n">
-        <v>0.7804</v>
+        <v>0.9441000000000001</v>
       </c>
     </row>
     <row r="59">
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>24.04</v>
+        <v>29.06</v>
       </c>
       <c r="C59" t="n">
-        <v>0.8077</v>
+        <v>0.9277</v>
       </c>
     </row>
     <row r="60">
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>20.77</v>
+        <v>24.82</v>
       </c>
       <c r="C60" t="n">
-        <v>0.6579</v>
+        <v>0.8463000000000001</v>
       </c>
     </row>
     <row r="61">
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>21.39</v>
+        <v>23.8</v>
       </c>
       <c r="C61" t="n">
-        <v>0.5492</v>
+        <v>0.6775</v>
       </c>
     </row>
     <row r="62">
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>23.74</v>
+        <v>26.93</v>
       </c>
       <c r="C62" t="n">
-        <v>0.709</v>
+        <v>0.852</v>
       </c>
     </row>
     <row r="63">
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>21.23</v>
+        <v>25.36</v>
       </c>
       <c r="C63" t="n">
-        <v>0.7533</v>
+        <v>0.9135</v>
       </c>
     </row>
     <row r="64">
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>19.83</v>
+        <v>24.42</v>
       </c>
       <c r="C64" t="n">
-        <v>0.5469000000000001</v>
+        <v>0.6776</v>
       </c>
     </row>
     <row r="65">
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>25.48</v>
+        <v>28.86</v>
       </c>
       <c r="C65" t="n">
-        <v>0.7637</v>
+        <v>0.8623</v>
       </c>
     </row>
     <row r="66">
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>24.66</v>
+        <v>27.63</v>
       </c>
       <c r="C66" t="n">
-        <v>0.7256</v>
+        <v>0.8377</v>
       </c>
     </row>
     <row r="67">
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>21.98</v>
+        <v>23.47</v>
       </c>
       <c r="C67" t="n">
-        <v>0.6425999999999999</v>
+        <v>0.7345</v>
       </c>
     </row>
     <row r="68">
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>18.64</v>
+        <v>22.73</v>
       </c>
       <c r="C68" t="n">
-        <v>0.7847</v>
+        <v>0.9328</v>
       </c>
     </row>
     <row r="69">
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>27.88</v>
+        <v>33.66</v>
       </c>
       <c r="C69" t="n">
-        <v>0.7922</v>
+        <v>0.9418</v>
       </c>
     </row>
     <row r="70">
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>23.51</v>
+        <v>26.44</v>
       </c>
       <c r="C70" t="n">
-        <v>0.7028</v>
+        <v>0.8328</v>
       </c>
     </row>
     <row r="71">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>21.86</v>
+        <v>23.15</v>
       </c>
       <c r="C71" t="n">
-        <v>0.5789</v>
+        <v>0.6785</v>
       </c>
     </row>
     <row r="72">
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>25.48</v>
+        <v>29.73</v>
       </c>
       <c r="C72" t="n">
-        <v>0.6163</v>
+        <v>0.7537</v>
       </c>
     </row>
     <row r="73">
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>18.27</v>
+        <v>23.06</v>
       </c>
       <c r="C73" t="n">
-        <v>0.7208</v>
+        <v>0.9024</v>
       </c>
     </row>
     <row r="74">
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>21.01</v>
+        <v>22.91</v>
       </c>
       <c r="C74" t="n">
-        <v>0.6248</v>
+        <v>0.7363</v>
       </c>
     </row>
     <row r="75">
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>22.63</v>
+        <v>25.98</v>
       </c>
       <c r="C75" t="n">
-        <v>0.6366000000000001</v>
+        <v>0.8322000000000001</v>
       </c>
     </row>
     <row r="76">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>26.68</v>
+        <v>33.86</v>
       </c>
       <c r="C76" t="n">
-        <v>0.7705</v>
+        <v>0.9152</v>
       </c>
     </row>
     <row r="77">
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>23.23</v>
+        <v>26.65</v>
       </c>
       <c r="C77" t="n">
-        <v>0.7204</v>
+        <v>0.8774</v>
       </c>
     </row>
     <row r="78">
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>22.2</v>
+        <v>23.84</v>
       </c>
       <c r="C78" t="n">
-        <v>0.6479</v>
+        <v>0.7579</v>
       </c>
     </row>
     <row r="79">
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>26.64</v>
+        <v>29.79</v>
       </c>
       <c r="C79" t="n">
-        <v>0.7215</v>
+        <v>0.8489</v>
       </c>
     </row>
     <row r="80">
@@ -1466,10 +1466,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>24.32</v>
+        <v>27.32</v>
       </c>
       <c r="C80" t="n">
-        <v>0.6701</v>
+        <v>0.7835</v>
       </c>
     </row>
     <row r="81">
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>29.94</v>
+        <v>37.69</v>
       </c>
       <c r="C81" t="n">
-        <v>0.8046</v>
+        <v>0.9694</v>
       </c>
     </row>
     <row r="82">
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>29.71</v>
+        <v>40.5</v>
       </c>
       <c r="C82" t="n">
-        <v>0.8814</v>
+        <v>0.9828</v>
       </c>
     </row>
     <row r="83">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>28.14</v>
+        <v>35.42</v>
       </c>
       <c r="C83" t="n">
-        <v>0.8367</v>
+        <v>0.959</v>
       </c>
     </row>
     <row r="84">
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>21.2</v>
+        <v>23.97</v>
       </c>
       <c r="C84" t="n">
-        <v>0.6548</v>
+        <v>0.8006</v>
       </c>
     </row>
     <row r="85">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>27.57</v>
+        <v>31.04</v>
       </c>
       <c r="C85" t="n">
-        <v>0.7657</v>
+        <v>0.8797</v>
       </c>
     </row>
     <row r="86">
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>27.42</v>
+        <v>30.75</v>
       </c>
       <c r="C86" t="n">
-        <v>0.7947</v>
+        <v>0.9432</v>
       </c>
     </row>
     <row r="87">
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>27.8</v>
+        <v>32.82</v>
       </c>
       <c r="C87" t="n">
-        <v>0.7932</v>
+        <v>0.924</v>
       </c>
     </row>
     <row r="88">
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>23.73</v>
+        <v>30.73</v>
       </c>
       <c r="C88" t="n">
-        <v>0.7445000000000001</v>
+        <v>0.9352</v>
       </c>
     </row>
     <row r="89">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>19.78</v>
+        <v>21.48</v>
       </c>
       <c r="C89" t="n">
-        <v>0.5762</v>
+        <v>0.7007</v>
       </c>
     </row>
     <row r="90">
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>25.93</v>
+        <v>28.46</v>
       </c>
       <c r="C90" t="n">
-        <v>0.7025</v>
+        <v>0.8082</v>
       </c>
     </row>
     <row r="91">
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>30.98</v>
+        <v>41.89</v>
       </c>
       <c r="C91" t="n">
-        <v>0.8266</v>
+        <v>0.9861</v>
       </c>
     </row>
     <row r="92">
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>23</v>
+        <v>26.03</v>
       </c>
       <c r="C92" t="n">
-        <v>0.6471</v>
+        <v>0.7998</v>
       </c>
     </row>
     <row r="93">
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>17.3</v>
+        <v>20.81</v>
       </c>
       <c r="C93" t="n">
-        <v>0.5365</v>
+        <v>0.7481</v>
       </c>
     </row>
     <row r="94">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>25.89</v>
+        <v>32.69</v>
       </c>
       <c r="C94" t="n">
-        <v>0.8357</v>
+        <v>0.9559</v>
       </c>
     </row>
     <row r="95">
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>26.19</v>
+        <v>28.7</v>
       </c>
       <c r="C95" t="n">
-        <v>0.7294</v>
+        <v>0.8433</v>
       </c>
     </row>
     <row r="96">
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>19.63</v>
+        <v>21.52</v>
       </c>
       <c r="C96" t="n">
-        <v>0.4517</v>
+        <v>0.5837</v>
       </c>
     </row>
     <row r="97">
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>22.63</v>
+        <v>28.68</v>
       </c>
       <c r="C97" t="n">
-        <v>0.7356</v>
+        <v>0.9294</v>
       </c>
     </row>
     <row r="98">
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>23.55</v>
+        <v>26.83</v>
       </c>
       <c r="C98" t="n">
-        <v>0.7126</v>
+        <v>0.8438</v>
       </c>
     </row>
     <row r="99">
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>20.51</v>
+        <v>22</v>
       </c>
       <c r="C99" t="n">
-        <v>0.5233</v>
+        <v>0.6553</v>
       </c>
     </row>
     <row r="100">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>23.47</v>
+        <v>28.73</v>
       </c>
       <c r="C100" t="n">
-        <v>0.6972</v>
+        <v>0.8837</v>
       </c>
     </row>
     <row r="101">
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>23.51</v>
+        <v>27.48</v>
       </c>
       <c r="C101" t="n">
-        <v>0.6545</v>
+        <v>0.7867</v>
       </c>
     </row>
     <row r="102">
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>23.9</v>
+        <v>28.35</v>
       </c>
       <c r="C102" t="n">
-        <v>0.7141999999999999</v>
+        <v>0.8567</v>
       </c>
     </row>
   </sheetData>
